--- a/backtest_runs/20260410_193731/by_symbol/GATM/GATM.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/GATM/GATM.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -541,7 +541,7 @@
         <v>-4252.800000000004</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>95747.2</v>
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="I5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>98989.95999999999</v>
@@ -771,7 +771,7 @@
         <v>-53.15999999998942</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>98936.8</v>
@@ -863,7 +863,7 @@
         <v>-691.0800000000136</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>98617.84</v>
@@ -909,7 +909,7 @@
         <v>-106.3199999999977</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>98511.51999999999</v>
@@ -998,10 +998,10 @@
         </is>
       </c>
       <c r="I12" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K12" s="3" t="n">
         <v>99096.27999999998</v>
@@ -1044,10 +1044,10 @@
         </is>
       </c>
       <c r="I13" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K13" s="3" t="n">
         <v>99096.27999999998</v>
@@ -1185,7 +1185,7 @@
         <v>-6219.71999999999</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>100265.8</v>
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="I17" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K17" s="3" t="n">
         <v>100265.8</v>
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="I18" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>100265.8</v>
@@ -1323,7 +1323,7 @@
         <v>-3455.400000000011</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>96810.39999999999</v>
@@ -1415,7 +1415,7 @@
         <v>-1382.160000000008</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>102126.4</v>
@@ -1461,7 +1461,7 @@
         <v>-850.5600000000007</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>101275.84</v>
@@ -1507,7 +1507,7 @@
         <v>-903.7199999999901</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>100372.12</v>
@@ -1550,10 +1550,10 @@
         </is>
       </c>
       <c r="I24" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K24" s="3" t="n">
         <v>100372.12</v>
